--- a/data/__enum__.xlsx
+++ b/data/__enum__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1020,13 +1020,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="16.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="13.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="15.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.375" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="27.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="19.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
@@ -1133,7 +1133,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1145,7 +1145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/__enum__.xlsx
+++ b/data/__enum__.xlsx
@@ -1,250 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>WeaponType</t>
-  </si>
-  <si>
-    <t>Dagger</t>
-  </si>
-  <si>
-    <t>小刀</t>
-  </si>
-  <si>
-    <t>Sword</t>
-  </si>
-  <si>
-    <t>剑</t>
-  </si>
-  <si>
-    <t>Wand</t>
-  </si>
-  <si>
-    <t>魔杖</t>
-  </si>
-  <si>
-    <t>Staff</t>
-  </si>
-  <si>
-    <t>法杖</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>NoneGender</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>男性</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>女性</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -550,164 +479,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -761,11 +689,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1017,138 +1008,1072 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="19.375" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="27.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.775" customWidth="1"/>
+    <col width="15.1111111111111" customWidth="1" style="2" min="1" max="1"/>
+    <col width="19.3796296296296" customWidth="1" style="2" min="2" max="2"/>
+    <col width="17.5" customWidth="1" style="2" min="3" max="3"/>
+    <col width="27.6666666666667" customWidth="1" style="2" min="4" max="4"/>
+    <col width="19.7777777777778" customWidth="1" style="2" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WeaponType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Dagger</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>小刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Wand</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>魔杖</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>法杖</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>NoneGender</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EquipmentSlot</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>头盔</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>BodyArmor</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>胸甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>手套</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>靴子</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>戒指</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Amulet</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>护身符</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="1" s="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EquipmentRarity</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>普通(白)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>魔法(蓝)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>稀有(黄)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>传奇(橙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="1" s="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>AffixSlotType</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Prefix</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>前缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Suffix</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>后缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>AdventurerRole</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Ranger</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>游侠</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Rogue</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>OrderType</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>WalkIn</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>散客订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>区域倾向订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>Guild</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>公会订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>OrderDifficulty</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>极限</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>ArchetypeDimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>PureDamage</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>纯输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>TankSurvival</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>肉盾生存</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>SupportHeal</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>辅助奶妈</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>CritBurst</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>暴击爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>DotSpread</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>持续蔓延</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>HybridComposite</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>复合构筑</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>OrderVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>SingleMissing</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>残缺拼图-单件</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>FullSet</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>完全体拼图-多件套</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>代工订单-锁底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>SquadDrill</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>实战编队演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>学徒改造锤</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Essence</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>定向元素精华</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Chisel</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>崇高打孔锥</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Sandpaper</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>神圣微调砂纸</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Drill</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>混沌重铸钻</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>VoidCore</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>虚空魔核</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>CurrencyEffect</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>RerollOne</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>重置单条词条(三选一)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>ForceTag</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>强制生成指定标签词条</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>AddSlot</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>追加新词条槽位</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>RerollValue</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>重Roll词条数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>RerollAll</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>重置全部词条</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>Corrupt</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>不可逆腐化变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SkillType</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>主动技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>质变被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OnCooldown</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>冷却完毕自动释放</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OnLowHp</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>低血量触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>暴击时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>击杀时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>受击时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>6</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>常驻生效</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/__enum__.xlsx
+++ b/data/__enum__.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.1111111111111" customWidth="1" style="2" min="1" max="1"/>
@@ -1026,7 +1026,7 @@
     <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>WeaponType</t>
+          <t>Gender</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Dagger</t>
+          <t>NoneGender</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>小刀</t>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Sword</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>剑</t>
+          <t>男性</t>
         </is>
       </c>
     </row>
@@ -1066,198 +1066,202 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Wand</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>魔杖</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>法杖</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
+          <t>女性</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EquipmentSlot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>武器</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>NoneGender</t>
+          <t>Helmet</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>头盔</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>BodyArmor</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>男性</t>
+          <t>胸甲</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Gloves</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>女性</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>EquipmentSlot</t>
+          <t>手套</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>靴子</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Ring</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>武器</t>
+          <t>戒指</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Helmet</t>
+          <t>Amulet</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>头盔</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>BodyArmor</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>胸甲</t>
-        </is>
-      </c>
+          <t>护身符</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EquipmentRarity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Gloves</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>手套</t>
+          <t>普通(白)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Boots</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>靴子</t>
+          <t>魔法(蓝)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Ring</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>戒指</t>
+          <t>稀有(黄)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Amulet</t>
+          <t>Unique</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>护身符</t>
+          <t>传奇(橙)</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>EquipmentRarity</t>
+          <t>AffixSlotType</t>
         </is>
       </c>
       <c r="B18" s="3" t="n"/>
@@ -1271,12 +1275,12 @@
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Prefix</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>普通(白)</t>
+          <t>前缀</t>
         </is>
       </c>
     </row>
@@ -1286,92 +1290,96 @@
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suffix</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>魔法(蓝)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>稀有(黄)</t>
-        </is>
-      </c>
+          <t>后缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="1" s="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>AdventurerRole</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>传奇(橙)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="1" s="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>AffixSlotType</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+          <t>战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Ranger</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>游侠</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>前缀</t>
+          <t>法师</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Suffix</t>
+          <t>Rogue</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>后缀</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>AdventurerRole</t>
-        </is>
-      </c>
+          <t>刺客</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="1" s="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>OrderType</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
@@ -1379,12 +1387,12 @@
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>WalkIn</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>战士</t>
+          <t>散客订单</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1402,12 @@
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Ranger</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>游侠</t>
+          <t>区域倾向订单</t>
         </is>
       </c>
     </row>
@@ -1409,88 +1417,96 @@
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Guild</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>Rogue</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>刺客</t>
-        </is>
-      </c>
+          <t>公会订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="1" s="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>OrderDifficulty</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>OrderType</t>
+      <c r="A31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>简单</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>WalkIn</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>散客订单</t>
+          <t>普通</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>区域倾向订单</t>
+          <t>困难</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>Guild</t>
+          <t>Extreme</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>公会订单</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t>OrderDifficulty</t>
-        </is>
-      </c>
+          <t>极限</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="1" s="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ArchetypeDimension</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
@@ -1498,12 +1514,12 @@
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>PureDamage</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>纯输出</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1529,12 @@
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>TankSurvival</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>肉盾生存</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1544,12 @@
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>SupportHeal</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>辅助奶妈</t>
         </is>
       </c>
     </row>
@@ -1543,118 +1559,126 @@
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>Extreme</t>
+          <t>CritBurst</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>极限</t>
+          <t>暴击爆发</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>ArchetypeDimension</t>
+      <c r="A40" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>DotSpread</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>持续蔓延</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>PureDamage</t>
+          <t>HybridComposite</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>纯输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>TankSurvival</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>肉盾生存</t>
-        </is>
-      </c>
+          <t>复合构筑</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="1" s="1">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>OrderVariant</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>SupportHeal</t>
+          <t>SingleMissing</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>辅助奶妈</t>
+          <t>残缺拼图-单件</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>CritBurst</t>
+          <t>FullSet</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>暴击爆发</t>
+          <t>完全体拼图-多件套</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>DotSpread</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>持续蔓延</t>
+          <t>代工订单-锁底材</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>HybridComposite</t>
+          <t>SquadDrill</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>复合构筑</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="inlineStr">
-        <is>
-          <t>OrderVariant</t>
-        </is>
-      </c>
+          <t>实战编队演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="1" s="1">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CurrencyType</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
@@ -1662,12 +1686,12 @@
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>SingleMissing</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>残缺拼图-单件</t>
+          <t>学徒改造锤</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1701,12 @@
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>FullSet</t>
+          <t>Essence</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>完全体拼图-多件套</t>
+          <t>定向元素精华</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1716,12 @@
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Chisel</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>代工订单-锁底材</t>
+          <t>崇高打孔锥</t>
         </is>
       </c>
     </row>
@@ -1707,340 +1731,1419 @@
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>SquadDrill</t>
+          <t>Sandpaper</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>实战编队演练</t>
+          <t>神圣微调砂纸</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="inlineStr">
-        <is>
-          <t>CurrencyType</t>
+      <c r="A52" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Drill</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>混沌重铸钻</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>VoidCore</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>学徒改造锤</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>Essence</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>定向元素精华</t>
-        </is>
-      </c>
+          <t>虚空魔核</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="1" s="1">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>CurrencyEffect</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>Chisel</t>
+          <t>RerollOne</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>崇高打孔锥</t>
+          <t>重置单条词条(三选一)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>Sandpaper</t>
+          <t>ForceTag</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>神圣微调砂纸</t>
+          <t>强制生成指定标签词条</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>AddSlot</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>混沌重铸钻</t>
+          <t>追加新词条槽位</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>VoidCore</t>
+          <t>RerollValue</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>虚空魔核</t>
+          <t>重Roll词条数值</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="0" t="inlineStr">
-        <is>
-          <t>CurrencyEffect</t>
+      <c r="A59" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>RerollAll</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>重置全部词条</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>RerollOne</t>
+          <t>Corrupt</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>重置单条词条(三选一)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>ForceTag</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>强制生成指定标签词条</t>
-        </is>
-      </c>
+          <t>不可逆腐化变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="1" s="1">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>SkillType</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AddSlot</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>追加新词条槽位</t>
+          <t>主动</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>RerollValue</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>重Roll词条数值</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B64" s="0" t="inlineStr">
-        <is>
-          <t>RerollAll</t>
-        </is>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>重置全部词条</t>
-        </is>
-      </c>
+          <t>被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="1" s="1">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>OnCooldown</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>冷却完毕自动释放</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>OnLowHp</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>低血量触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>暴击时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>击杀时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>受击时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>Corrupt</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="inlineStr">
-        <is>
-          <t>不可逆腐化变异</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>SkillType</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>常驻生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="1" s="1">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>主动技能</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>攻击力-基础点伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>质变被动</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>SkillTrigger</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>护甲-物理减伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>最大生命值</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>攻击速度-动作速率</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>CritDmgMultiplier</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>暴击伤害倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>CooldownReduction</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>冷却缩减</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>IncreasedDamage</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>A类增伤(同类相加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>MoreDamage</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>B类独立乘区伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>IncreasedArmor</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>A类增防(同类相加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>MoreArmor</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>B类独立乘区防御</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>HealPower</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>治疗强度</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>MoreHeal</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>B类独立乘区治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>FireResist</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>火焰抗性</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>IceResist</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>冰霜抗性</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>PoisonResist</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>毒素抗性</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>DotDamage</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>持续伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>AoERadius</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>AOE范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" customFormat="1" s="1">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>TraitType</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OnCooldown</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>冷却完毕自动释放</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>IronWill</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>坚韧意志-受伤减免</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>FirstStrike</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>先手优势-开局爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>ArcaneAffinity</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>奥术亲和-法术增幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>LethalStrike</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>致命一击-必定暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>CritMultiplier</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>暴伤翻倍-暴击伤害乘区</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>ArmorCounter</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>破甲反击-受击触发反击</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>Undying</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>不死之身-低血量无敌护盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>PoisonBlade</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>毒刃-命中附加毒伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>Regeneration</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>生命涌泉-持续回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>WarCry</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>战吼-全队增伤光环</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" customFormat="1" s="1">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>MaterialTag</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>武器类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>剑类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>Dagger</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>匕首类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t>Wand</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>法杖类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>长杖类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>BodyArmor</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>胸甲类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>头盔类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>手套类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>靴子类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>戒指类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Amulet</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>项链类底材</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" customFormat="1" s="1">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>SceneType</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n"/>
+      <c r="C114" s="3" t="n"/>
+      <c r="D114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>竞技场-标准战斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>堡垒-防守战</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Endurance</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>耐力试炼-生存挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Swarm</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>虫群-大量敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>Boss战-单体强敌</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Dungeon</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>地下城-综合挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" customFormat="1" s="1">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>SquadRole</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n"/>
+      <c r="C121" s="3" t="n"/>
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>MainDps</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>RangerDps</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>远程输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>MageDps</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>法师输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>坦克</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>辅助</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>Healer</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TraitTriggerType</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>常驻被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>OnCombatStart</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>战斗开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>暴击时</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>命中时</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>击杀时</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>6</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>OnDamageTaken</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>受伤时</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" t="inlineStr">
         <is>
           <t>OnLowHp</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>低血量触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>低血量时</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>8</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>OnHeal</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>治疗时</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>9</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OnDeath</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>死亡时</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TraitEffectType</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>StatMultiplier</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>属性乘区(B类独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>StatAdditive</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>属性加成(A类相加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
         <v>3</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OnCrit</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>暴击时触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ForceCrit</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>强制暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
         <v>4</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OnKill</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>击杀时触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Immunity</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>免疫/无敌</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
         <v>5</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>受击时触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Dot</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>持续伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
         <v>6</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>常驻生效</t>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>7</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>光环(全队)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>9</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>10</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dispel</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>驱散</t>
         </is>
       </c>
     </row>
